--- a/Models/Овцы и козы/Датасет по овцы и козы wide.xlsx
+++ b/Models/Овцы и козы/Датасет по овцы и козы wide.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7877,6 +7877,475 @@
         <v>8866.360000000001</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>606.5599999999999</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1267.28</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1113.56</v>
+      </c>
+      <c r="E122" t="n">
+        <v>488.5500000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>516.73</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I122" t="n">
+        <v>108.39</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1880.47</v>
+      </c>
+      <c r="K122" t="n">
+        <v>595.6700000000001</v>
+      </c>
+      <c r="L122" t="n">
+        <v>381</v>
+      </c>
+      <c r="M122" t="n">
+        <v>330.86</v>
+      </c>
+      <c r="N122" t="n">
+        <v>533.78</v>
+      </c>
+      <c r="O122" t="n">
+        <v>151.54</v>
+      </c>
+      <c r="P122" t="n">
+        <v>612.23</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>689.58</v>
+      </c>
+      <c r="R122" t="n">
+        <v>338.6</v>
+      </c>
+      <c r="S122" t="n">
+        <v>392.03</v>
+      </c>
+      <c r="T122" t="n">
+        <v>328.67</v>
+      </c>
+      <c r="U122" t="n">
+        <v>4447.97</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>807.76</v>
+      </c>
+      <c r="C123" t="n">
+        <v>536.79</v>
+      </c>
+      <c r="D123" t="n">
+        <v>526.89</v>
+      </c>
+      <c r="E123" t="n">
+        <v>574.5999999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>716.8</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I123" t="n">
+        <v>76.72</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1806.25</v>
+      </c>
+      <c r="K123" t="n">
+        <v>629.36</v>
+      </c>
+      <c r="L123" t="n">
+        <v>375.04</v>
+      </c>
+      <c r="M123" t="n">
+        <v>141.87</v>
+      </c>
+      <c r="N123" t="n">
+        <v>474.22</v>
+      </c>
+      <c r="O123" t="n">
+        <v>157.54</v>
+      </c>
+      <c r="P123" t="n">
+        <v>873.9499999999999</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>634.3099999999999</v>
+      </c>
+      <c r="R123" t="n">
+        <v>294.8</v>
+      </c>
+      <c r="S123" t="n">
+        <v>423.63</v>
+      </c>
+      <c r="T123" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="U123" t="n">
+        <v>4266.88</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>799.6799999999999</v>
+      </c>
+      <c r="C124" t="n">
+        <v>2929.62</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3722.4</v>
+      </c>
+      <c r="E124" t="n">
+        <v>986.8299999999999</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1048.98</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I124" t="n">
+        <v>63.56</v>
+      </c>
+      <c r="J124" t="n">
+        <v>2109.5</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1093.13</v>
+      </c>
+      <c r="L124" t="n">
+        <v>837.54</v>
+      </c>
+      <c r="M124" t="n">
+        <v>179.06</v>
+      </c>
+      <c r="N124" t="n">
+        <v>443.29</v>
+      </c>
+      <c r="O124" t="n">
+        <v>131.34</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1305.68</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>3323.46</v>
+      </c>
+      <c r="R124" t="n">
+        <v>306.9</v>
+      </c>
+      <c r="S124" t="n">
+        <v>527.4400000000001</v>
+      </c>
+      <c r="T124" t="n">
+        <v>226.5</v>
+      </c>
+      <c r="U124" t="n">
+        <v>4540.22</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>798.4</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1795.06</v>
+      </c>
+      <c r="D125" t="n">
+        <v>775.3299999999999</v>
+      </c>
+      <c r="E125" t="n">
+        <v>812.85</v>
+      </c>
+      <c r="F125" t="n">
+        <v>832.48</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I125" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="J125" t="n">
+        <v>2102.1</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1348</v>
+      </c>
+      <c r="L125" t="n">
+        <v>357.73</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1433.99</v>
+      </c>
+      <c r="N125" t="n">
+        <v>309.81</v>
+      </c>
+      <c r="O125" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="P125" t="n">
+        <v>1741.28</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>811.6800000000001</v>
+      </c>
+      <c r="R125" t="n">
+        <v>261.8</v>
+      </c>
+      <c r="S125" t="n">
+        <v>904.24</v>
+      </c>
+      <c r="T125" t="n">
+        <v>324.2</v>
+      </c>
+      <c r="U125" t="n">
+        <v>3939.72</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>819.9499999999999</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1235.48</v>
+      </c>
+      <c r="D126" t="n">
+        <v>937.0599999999999</v>
+      </c>
+      <c r="E126" t="n">
+        <v>755.9300000000001</v>
+      </c>
+      <c r="F126" t="n">
+        <v>946.63</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I126" t="n">
+        <v>48</v>
+      </c>
+      <c r="J126" t="n">
+        <v>2455.4</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1610.72</v>
+      </c>
+      <c r="L126" t="n">
+        <v>1127.95</v>
+      </c>
+      <c r="M126" t="n">
+        <v>149.31</v>
+      </c>
+      <c r="N126" t="n">
+        <v>628.26</v>
+      </c>
+      <c r="O126" t="n">
+        <v>132.39</v>
+      </c>
+      <c r="P126" t="n">
+        <v>2006.25</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>643.8</v>
+      </c>
+      <c r="R126" t="n">
+        <v>699</v>
+      </c>
+      <c r="S126" t="n">
+        <v>819.04</v>
+      </c>
+      <c r="T126" t="n">
+        <v>431.65</v>
+      </c>
+      <c r="U126" t="n">
+        <v>3631.9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>909.79</v>
+      </c>
+      <c r="C127" t="n">
+        <v>2052.14</v>
+      </c>
+      <c r="D127" t="n">
+        <v>3243.32</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2961.75</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1415.91</v>
+      </c>
+      <c r="G127" t="n">
+        <v>5</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I127" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J127" t="n">
+        <v>4804</v>
+      </c>
+      <c r="K127" t="n">
+        <v>2238.47</v>
+      </c>
+      <c r="L127" t="n">
+        <v>2110.63</v>
+      </c>
+      <c r="M127" t="n">
+        <v>133.92</v>
+      </c>
+      <c r="N127" t="n">
+        <v>526.6799999999999</v>
+      </c>
+      <c r="O127" t="n">
+        <v>207.71</v>
+      </c>
+      <c r="P127" t="n">
+        <v>4668.04</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>4021.84</v>
+      </c>
+      <c r="R127" t="n">
+        <v>794.2</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1158.24</v>
+      </c>
+      <c r="T127" t="n">
+        <v>492.27</v>
+      </c>
+      <c r="U127" t="n">
+        <v>3915</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>525.54</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1244.06</v>
+      </c>
+      <c r="D128" t="n">
+        <v>950.9300000000001</v>
+      </c>
+      <c r="E128" t="n">
+        <v>744.45</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1527.06</v>
+      </c>
+      <c r="G128" t="n">
+        <v>6</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>128.01</v>
+      </c>
+      <c r="J128" t="n">
+        <v>2430.85</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1548.44</v>
+      </c>
+      <c r="L128" t="n">
+        <v>518.05</v>
+      </c>
+      <c r="M128" t="n">
+        <v>153.09</v>
+      </c>
+      <c r="N128" t="n">
+        <v>250.73</v>
+      </c>
+      <c r="O128" t="n">
+        <v>176.88</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1030.78</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>801.7900000000001</v>
+      </c>
+      <c r="R128" t="n">
+        <v>246.9</v>
+      </c>
+      <c r="S128" t="n">
+        <v>573.3</v>
+      </c>
+      <c r="T128" t="n">
+        <v>989.64</v>
+      </c>
+      <c r="U128" t="n">
+        <v>2576.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
